--- a/results/momentum_strong_2026-09-29.xlsx
+++ b/results/momentum_strong_2026-09-29.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D170"/>
+  <dimension ref="A1:D162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -441,7 +441,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>AERT</t>
+          <t>CHAD</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -451,19 +451,19 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>ONCO</t>
+          <t>NEON</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>ACGLO</t>
+          <t>AEHL</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>AGEN</t>
+          <t>COSM</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -471,346 +471,334 @@
           <t>ABLV</t>
         </is>
       </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>RDNW</t>
-        </is>
-      </c>
+      <c r="C3" t="inlineStr"/>
       <c r="D3" t="inlineStr">
         <is>
-          <t>AZN</t>
+          <t>AER</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>AUDC</t>
+          <t>FJDIU</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>ACU</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>RFAMU</t>
-        </is>
-      </c>
+          <t>ACRV</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>BLNK</t>
+          <t>AMKR</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>BNKK</t>
+          <t>IOVA</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>ADAMG</t>
+          <t>ADI</t>
         </is>
       </c>
       <c r="C5" t="inlineStr"/>
       <c r="D5" t="inlineStr">
         <is>
-          <t>BPRE</t>
+          <t>AUUD</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>BRKRP</t>
+          <t>LINK</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>ADI</t>
+          <t>AERT</t>
         </is>
       </c>
       <c r="C6" t="inlineStr"/>
       <c r="D6" t="inlineStr">
         <is>
-          <t>COLA</t>
+          <t>CAMT</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>CHSCO</t>
+          <t>NTWK</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>ADMA</t>
+          <t>AGEN</t>
         </is>
       </c>
       <c r="C7" t="inlineStr"/>
       <c r="D7" t="inlineStr">
         <is>
-          <t>CRUS</t>
+          <t>CBRS</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>GGR</t>
+          <t>QSI</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>AEMD</t>
+          <t>AGPU</t>
         </is>
       </c>
       <c r="C8" t="inlineStr"/>
       <c r="D8" t="inlineStr">
         <is>
-          <t>DOMH</t>
+          <t>COLA</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>HBIO</t>
+          <t>SDEV</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>ALVO</t>
+          <t>AIIA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>FAC</t>
+          <t>CRUS</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>LAFA</t>
+          <t>SXTP</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>ALZN</t>
+          <t>ALP</t>
         </is>
       </c>
       <c r="C10" t="inlineStr"/>
       <c r="D10" t="inlineStr">
         <is>
-          <t>IQST</t>
+          <t>GCDT</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>MEDS</t>
+          <t>TACH</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>AMBR</t>
+          <t>ARW</t>
         </is>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>MWC</t>
+          <t>GNLN</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>MTLS</t>
+          <t>XRPN</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>AMPH</t>
+          <t>ASBH</t>
         </is>
       </c>
       <c r="C12" t="inlineStr"/>
       <c r="D12" t="inlineStr">
         <is>
-          <t>OCC</t>
+          <t>GRDX</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>NRSN</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
-          <t>AMRX</t>
+          <t>ASML</t>
         </is>
       </c>
       <c r="C13" t="inlineStr"/>
       <c r="D13" t="inlineStr">
         <is>
-          <t>QMLS</t>
+          <t>KLAC</t>
         </is>
       </c>
     </row>
     <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>NTWK</t>
-        </is>
-      </c>
+      <c r="A14" t="inlineStr"/>
       <c r="B14" t="inlineStr">
         <is>
-          <t>ARQT</t>
+          <t>ASST</t>
         </is>
       </c>
       <c r="C14" t="inlineStr"/>
       <c r="D14" t="inlineStr">
         <is>
-          <t>SSYS</t>
+          <t>MSS</t>
         </is>
       </c>
     </row>
     <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>PACB</t>
-        </is>
-      </c>
+      <c r="A15" t="inlineStr"/>
       <c r="B15" t="inlineStr">
         <is>
-          <t>ASML</t>
+          <t>ASYS</t>
         </is>
       </c>
       <c r="C15" t="inlineStr"/>
       <c r="D15" t="inlineStr">
         <is>
-          <t>SWRD</t>
+          <t>MWC</t>
         </is>
       </c>
     </row>
     <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>PCAP</t>
-        </is>
-      </c>
+      <c r="A16" t="inlineStr"/>
       <c r="B16" t="inlineStr">
         <is>
+          <t>ATEC</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>OCC</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr"/>
+      <c r="B17" t="inlineStr">
+        <is>
           <t>ATKR</t>
         </is>
       </c>
-      <c r="C16" t="inlineStr"/>
-      <c r="D16" t="inlineStr"/>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>SBMT</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>ATRC</t>
-        </is>
-      </c>
       <c r="C17" t="inlineStr"/>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>PDC</t>
+        </is>
+      </c>
     </row>
     <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>SDEV</t>
-        </is>
-      </c>
+      <c r="A18" t="inlineStr"/>
       <c r="B18" t="inlineStr">
         <is>
-          <t>AZTA</t>
+          <t>ATLCL</t>
         </is>
       </c>
       <c r="C18" t="inlineStr"/>
-      <c r="D18" t="inlineStr"/>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>PLAB</t>
+        </is>
+      </c>
     </row>
     <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>SINT</t>
-        </is>
-      </c>
+      <c r="A19" t="inlineStr"/>
       <c r="B19" t="inlineStr">
         <is>
-          <t>BAND</t>
+          <t>ATLCZ</t>
         </is>
       </c>
       <c r="C19" t="inlineStr"/>
-      <c r="D19" t="inlineStr"/>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>POM</t>
+        </is>
+      </c>
     </row>
     <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>SONM</t>
-        </is>
-      </c>
+      <c r="A20" t="inlineStr"/>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BATRA</t>
+          <t>AUC</t>
         </is>
       </c>
       <c r="C20" t="inlineStr"/>
-      <c r="D20" t="inlineStr"/>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>RDNW</t>
+        </is>
+      </c>
     </row>
     <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>WSHP</t>
-        </is>
-      </c>
+      <c r="A21" t="inlineStr"/>
       <c r="B21" t="inlineStr">
         <is>
-          <t>BCSS</t>
+          <t>AVAT</t>
         </is>
       </c>
       <c r="C21" t="inlineStr"/>
-      <c r="D21" t="inlineStr"/>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>RXT</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr"/>
       <c r="B22" t="inlineStr">
         <is>
-          <t>BDSX</t>
+          <t>AVX</t>
         </is>
       </c>
       <c r="C22" t="inlineStr"/>
-      <c r="D22" t="inlineStr"/>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>SHLS</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr"/>
       <c r="B23" t="inlineStr">
         <is>
-          <t>BFRG</t>
+          <t>AXTI</t>
         </is>
       </c>
       <c r="C23" t="inlineStr"/>
-      <c r="D23" t="inlineStr"/>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>SPHL</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr"/>
       <c r="B24" t="inlineStr">
         <is>
-          <t>BHFAL</t>
+          <t>BCHT</t>
         </is>
       </c>
       <c r="C24" t="inlineStr"/>
@@ -820,7 +808,7 @@
       <c r="A25" t="inlineStr"/>
       <c r="B25" t="inlineStr">
         <is>
-          <t>BIIB</t>
+          <t>BCSS</t>
         </is>
       </c>
       <c r="C25" t="inlineStr"/>
@@ -830,7 +818,7 @@
       <c r="A26" t="inlineStr"/>
       <c r="B26" t="inlineStr">
         <is>
-          <t>BLFS</t>
+          <t>BMNP</t>
         </is>
       </c>
       <c r="C26" t="inlineStr"/>
@@ -840,7 +828,7 @@
       <c r="A27" t="inlineStr"/>
       <c r="B27" t="inlineStr">
         <is>
-          <t>BMNP</t>
+          <t>BNR</t>
         </is>
       </c>
       <c r="C27" t="inlineStr"/>
@@ -850,7 +838,7 @@
       <c r="A28" t="inlineStr"/>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BNGO</t>
+          <t>BPRE</t>
         </is>
       </c>
       <c r="C28" t="inlineStr"/>
@@ -860,7 +848,7 @@
       <c r="A29" t="inlineStr"/>
       <c r="B29" t="inlineStr">
         <is>
-          <t>BSVN</t>
+          <t>BTCS</t>
         </is>
       </c>
       <c r="C29" t="inlineStr"/>
@@ -870,7 +858,7 @@
       <c r="A30" t="inlineStr"/>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BWMN</t>
+          <t>BURU</t>
         </is>
       </c>
       <c r="C30" t="inlineStr"/>
@@ -880,7 +868,7 @@
       <c r="A31" t="inlineStr"/>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CAI</t>
+          <t>BWIN</t>
         </is>
       </c>
       <c r="C31" t="inlineStr"/>
@@ -890,7 +878,7 @@
       <c r="A32" t="inlineStr"/>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CBAT</t>
+          <t>BWMN</t>
         </is>
       </c>
       <c r="C32" t="inlineStr"/>
@@ -900,7 +888,7 @@
       <c r="A33" t="inlineStr"/>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CCNEP</t>
+          <t>CAI</t>
         </is>
       </c>
       <c r="C33" t="inlineStr"/>
@@ -910,7 +898,7 @@
       <c r="A34" t="inlineStr"/>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CD</t>
+          <t>CAN</t>
         </is>
       </c>
       <c r="C34" t="inlineStr"/>
@@ -920,7 +908,7 @@
       <c r="A35" t="inlineStr"/>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CDNA</t>
+          <t>CDRO</t>
         </is>
       </c>
       <c r="C35" t="inlineStr"/>
@@ -930,7 +918,7 @@
       <c r="A36" t="inlineStr"/>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CERT</t>
+          <t>CEVA</t>
         </is>
       </c>
       <c r="C36" t="inlineStr"/>
@@ -940,7 +928,7 @@
       <c r="A37" t="inlineStr"/>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CHEC</t>
+          <t>CHOW</t>
         </is>
       </c>
       <c r="C37" t="inlineStr"/>
@@ -950,7 +938,7 @@
       <c r="A38" t="inlineStr"/>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CHOW</t>
+          <t>CHSCL</t>
         </is>
       </c>
       <c r="C38" t="inlineStr"/>
@@ -960,7 +948,7 @@
       <c r="A39" t="inlineStr"/>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CLMB</t>
+          <t>CHSCO</t>
         </is>
       </c>
       <c r="C39" t="inlineStr"/>
@@ -970,7 +958,7 @@
       <c r="A40" t="inlineStr"/>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CNET</t>
+          <t>CLGN</t>
         </is>
       </c>
       <c r="C40" t="inlineStr"/>
@@ -980,7 +968,7 @@
       <c r="A41" t="inlineStr"/>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CNTN</t>
+          <t>CNET</t>
         </is>
       </c>
       <c r="C41" t="inlineStr"/>
@@ -1000,7 +988,7 @@
       <c r="A43" t="inlineStr"/>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CODA</t>
+          <t>COIN</t>
         </is>
       </c>
       <c r="C43" t="inlineStr"/>
@@ -1010,7 +998,7 @@
       <c r="A44" t="inlineStr"/>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CPOP</t>
+          <t>CPIX</t>
         </is>
       </c>
       <c r="C44" t="inlineStr"/>
@@ -1020,7 +1008,7 @@
       <c r="A45" t="inlineStr"/>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CRCT</t>
+          <t>CPOP</t>
         </is>
       </c>
       <c r="C45" t="inlineStr"/>
@@ -1030,7 +1018,7 @@
       <c r="A46" t="inlineStr"/>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CRON</t>
+          <t>CURX</t>
         </is>
       </c>
       <c r="C46" t="inlineStr"/>
@@ -1040,7 +1028,7 @@
       <c r="A47" t="inlineStr"/>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CRVL</t>
+          <t>DGII</t>
         </is>
       </c>
       <c r="C47" t="inlineStr"/>
@@ -1050,7 +1038,7 @@
       <c r="A48" t="inlineStr"/>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CSTL</t>
+          <t>DIOD</t>
         </is>
       </c>
       <c r="C48" t="inlineStr"/>
@@ -1060,7 +1048,7 @@
       <c r="A49" t="inlineStr"/>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CUB</t>
+          <t>DJCO</t>
         </is>
       </c>
       <c r="C49" t="inlineStr"/>
@@ -1070,7 +1058,7 @@
       <c r="A50" t="inlineStr"/>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CURI</t>
+          <t>DJT</t>
         </is>
       </c>
       <c r="C50" t="inlineStr"/>
@@ -1080,7 +1068,7 @@
       <c r="A51" t="inlineStr"/>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVLT</t>
+          <t>DXPE</t>
         </is>
       </c>
       <c r="C51" t="inlineStr"/>
@@ -1090,7 +1078,7 @@
       <c r="A52" t="inlineStr"/>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CWD</t>
+          <t>EDHL</t>
         </is>
       </c>
       <c r="C52" t="inlineStr"/>
@@ -1100,7 +1088,7 @@
       <c r="A53" t="inlineStr"/>
       <c r="B53" t="inlineStr">
         <is>
-          <t>DDOG</t>
+          <t>EEIQ</t>
         </is>
       </c>
       <c r="C53" t="inlineStr"/>
@@ -1110,7 +1098,7 @@
       <c r="A54" t="inlineStr"/>
       <c r="B54" t="inlineStr">
         <is>
-          <t>DJCO</t>
+          <t>EFSI</t>
         </is>
       </c>
       <c r="C54" t="inlineStr"/>
@@ -1120,7 +1108,7 @@
       <c r="A55" t="inlineStr"/>
       <c r="B55" t="inlineStr">
         <is>
-          <t>DMAA</t>
+          <t>EGBN</t>
         </is>
       </c>
       <c r="C55" t="inlineStr"/>
@@ -1130,7 +1118,7 @@
       <c r="A56" t="inlineStr"/>
       <c r="B56" t="inlineStr">
         <is>
-          <t>DMAC</t>
+          <t>ENGS</t>
         </is>
       </c>
       <c r="C56" t="inlineStr"/>
@@ -1140,7 +1128,7 @@
       <c r="A57" t="inlineStr"/>
       <c r="B57" t="inlineStr">
         <is>
-          <t>DSGR</t>
+          <t>ENTG</t>
         </is>
       </c>
       <c r="C57" t="inlineStr"/>
@@ -1150,7 +1138,7 @@
       <c r="A58" t="inlineStr"/>
       <c r="B58" t="inlineStr">
         <is>
-          <t>DXPE</t>
+          <t>EPRX</t>
         </is>
       </c>
       <c r="C58" t="inlineStr"/>
@@ -1160,7 +1148,7 @@
       <c r="A59" t="inlineStr"/>
       <c r="B59" t="inlineStr">
         <is>
-          <t>EBAY</t>
+          <t>FBLA</t>
         </is>
       </c>
       <c r="C59" t="inlineStr"/>
@@ -1170,7 +1158,7 @@
       <c r="A60" t="inlineStr"/>
       <c r="B60" t="inlineStr">
         <is>
-          <t>ECX</t>
+          <t>FEAM</t>
         </is>
       </c>
       <c r="C60" t="inlineStr"/>
@@ -1180,7 +1168,7 @@
       <c r="A61" t="inlineStr"/>
       <c r="B61" t="inlineStr">
         <is>
-          <t>EDTK</t>
+          <t>FLXS</t>
         </is>
       </c>
       <c r="C61" t="inlineStr"/>
@@ -1190,7 +1178,7 @@
       <c r="A62" t="inlineStr"/>
       <c r="B62" t="inlineStr">
         <is>
-          <t>EMBC</t>
+          <t>FORM</t>
         </is>
       </c>
       <c r="C62" t="inlineStr"/>
@@ -1200,7 +1188,7 @@
       <c r="A63" t="inlineStr"/>
       <c r="B63" t="inlineStr">
         <is>
-          <t>ENGS</t>
+          <t>FSBW</t>
         </is>
       </c>
       <c r="C63" t="inlineStr"/>
@@ -1210,7 +1198,7 @@
       <c r="A64" t="inlineStr"/>
       <c r="B64" t="inlineStr">
         <is>
-          <t>EXEL</t>
+          <t>GCL</t>
         </is>
       </c>
       <c r="C64" t="inlineStr"/>
@@ -1220,7 +1208,7 @@
       <c r="A65" t="inlineStr"/>
       <c r="B65" t="inlineStr">
         <is>
-          <t>FFIV</t>
+          <t>GLND</t>
         </is>
       </c>
       <c r="C65" t="inlineStr"/>
@@ -1230,7 +1218,7 @@
       <c r="A66" t="inlineStr"/>
       <c r="B66" t="inlineStr">
         <is>
-          <t>FRNM</t>
+          <t>GRI</t>
         </is>
       </c>
       <c r="C66" t="inlineStr"/>
@@ -1240,7 +1228,7 @@
       <c r="A67" t="inlineStr"/>
       <c r="B67" t="inlineStr">
         <is>
-          <t>FSBW</t>
+          <t>GTBP</t>
         </is>
       </c>
       <c r="C67" t="inlineStr"/>
@@ -1250,7 +1238,7 @@
       <c r="A68" t="inlineStr"/>
       <c r="B68" t="inlineStr">
         <is>
-          <t>FTRE</t>
+          <t>GYRE</t>
         </is>
       </c>
       <c r="C68" t="inlineStr"/>
@@ -1260,7 +1248,7 @@
       <c r="A69" t="inlineStr"/>
       <c r="B69" t="inlineStr">
         <is>
-          <t>GCL</t>
+          <t>HBIO</t>
         </is>
       </c>
       <c r="C69" t="inlineStr"/>
@@ -1270,7 +1258,7 @@
       <c r="A70" t="inlineStr"/>
       <c r="B70" t="inlineStr">
         <is>
-          <t>GEGGL</t>
+          <t>HITI</t>
         </is>
       </c>
       <c r="C70" t="inlineStr"/>
@@ -1280,7 +1268,7 @@
       <c r="A71" t="inlineStr"/>
       <c r="B71" t="inlineStr">
         <is>
-          <t>GH</t>
+          <t>HQI</t>
         </is>
       </c>
       <c r="C71" t="inlineStr"/>
@@ -1290,7 +1278,7 @@
       <c r="A72" t="inlineStr"/>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GILD</t>
+          <t>HSDT</t>
         </is>
       </c>
       <c r="C72" t="inlineStr"/>
@@ -1300,7 +1288,7 @@
       <c r="A73" t="inlineStr"/>
       <c r="B73" t="inlineStr">
         <is>
-          <t>GIW</t>
+          <t>IBEX</t>
         </is>
       </c>
       <c r="C73" t="inlineStr"/>
@@ -1310,7 +1298,7 @@
       <c r="A74" t="inlineStr"/>
       <c r="B74" t="inlineStr">
         <is>
-          <t>GLSI</t>
+          <t>IBRX</t>
         </is>
       </c>
       <c r="C74" t="inlineStr"/>
@@ -1320,7 +1308,7 @@
       <c r="A75" t="inlineStr"/>
       <c r="B75" t="inlineStr">
         <is>
-          <t>GMAB</t>
+          <t>IFBD</t>
         </is>
       </c>
       <c r="C75" t="inlineStr"/>
@@ -1330,7 +1318,7 @@
       <c r="A76" t="inlineStr"/>
       <c r="B76" t="inlineStr">
         <is>
-          <t>GRAL</t>
+          <t>III</t>
         </is>
       </c>
       <c r="C76" t="inlineStr"/>
@@ -1340,7 +1328,7 @@
       <c r="A77" t="inlineStr"/>
       <c r="B77" t="inlineStr">
         <is>
-          <t>GTBP</t>
+          <t>INAB</t>
         </is>
       </c>
       <c r="C77" t="inlineStr"/>
@@ -1350,7 +1338,7 @@
       <c r="A78" t="inlineStr"/>
       <c r="B78" t="inlineStr">
         <is>
-          <t>GYRE</t>
+          <t>IOND</t>
         </is>
       </c>
       <c r="C78" t="inlineStr"/>
@@ -1360,7 +1348,7 @@
       <c r="A79" t="inlineStr"/>
       <c r="B79" t="inlineStr">
         <is>
-          <t>HCM</t>
+          <t>IOSP</t>
         </is>
       </c>
       <c r="C79" t="inlineStr"/>
@@ -1370,7 +1358,7 @@
       <c r="A80" t="inlineStr"/>
       <c r="B80" t="inlineStr">
         <is>
-          <t>HLP</t>
+          <t>KAZR</t>
         </is>
       </c>
       <c r="C80" t="inlineStr"/>
@@ -1380,7 +1368,7 @@
       <c r="A81" t="inlineStr"/>
       <c r="B81" t="inlineStr">
         <is>
-          <t>IBRX</t>
+          <t>KLIC</t>
         </is>
       </c>
       <c r="C81" t="inlineStr"/>
@@ -1390,7 +1378,7 @@
       <c r="A82" t="inlineStr"/>
       <c r="B82" t="inlineStr">
         <is>
-          <t>III</t>
+          <t>KMDA</t>
         </is>
       </c>
       <c r="C82" t="inlineStr"/>
@@ -1400,7 +1388,7 @@
       <c r="A83" t="inlineStr"/>
       <c r="B83" t="inlineStr">
         <is>
-          <t>IMPPP</t>
+          <t>KMTS</t>
         </is>
       </c>
       <c r="C83" t="inlineStr"/>
@@ -1410,7 +1398,7 @@
       <c r="A84" t="inlineStr"/>
       <c r="B84" t="inlineStr">
         <is>
-          <t>INAB</t>
+          <t>LAUR</t>
         </is>
       </c>
       <c r="C84" t="inlineStr"/>
@@ -1420,7 +1408,7 @@
       <c r="A85" t="inlineStr"/>
       <c r="B85" t="inlineStr">
         <is>
-          <t>INOD</t>
+          <t>LITE</t>
         </is>
       </c>
       <c r="C85" t="inlineStr"/>
@@ -1430,7 +1418,7 @@
       <c r="A86" t="inlineStr"/>
       <c r="B86" t="inlineStr">
         <is>
-          <t>IOND</t>
+          <t>LRCX</t>
         </is>
       </c>
       <c r="C86" t="inlineStr"/>
@@ -1440,7 +1428,7 @@
       <c r="A87" t="inlineStr"/>
       <c r="B87" t="inlineStr">
         <is>
-          <t>IOSP</t>
+          <t>LTRX</t>
         </is>
       </c>
       <c r="C87" t="inlineStr"/>
@@ -1450,7 +1438,7 @@
       <c r="A88" t="inlineStr"/>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IOVA</t>
+          <t>MATH</t>
         </is>
       </c>
       <c r="C88" t="inlineStr"/>
@@ -1460,7 +1448,7 @@
       <c r="A89" t="inlineStr"/>
       <c r="B89" t="inlineStr">
         <is>
-          <t>ISRG</t>
+          <t>MCHP</t>
         </is>
       </c>
       <c r="C89" t="inlineStr"/>
@@ -1470,7 +1458,7 @@
       <c r="A90" t="inlineStr"/>
       <c r="B90" t="inlineStr">
         <is>
-          <t>IVVD</t>
+          <t>MCHPP</t>
         </is>
       </c>
       <c r="C90" t="inlineStr"/>
@@ -1480,7 +1468,7 @@
       <c r="A91" t="inlineStr"/>
       <c r="B91" t="inlineStr">
         <is>
-          <t>JOYY</t>
+          <t>MQ</t>
         </is>
       </c>
       <c r="C91" t="inlineStr"/>
@@ -1490,7 +1478,7 @@
       <c r="A92" t="inlineStr"/>
       <c r="B92" t="inlineStr">
         <is>
-          <t>JRSH</t>
+          <t>MRAM</t>
         </is>
       </c>
       <c r="C92" t="inlineStr"/>
@@ -1500,7 +1488,7 @@
       <c r="A93" t="inlineStr"/>
       <c r="B93" t="inlineStr">
         <is>
-          <t>JTAI</t>
+          <t>MTC</t>
         </is>
       </c>
       <c r="C93" t="inlineStr"/>
@@ -1510,7 +1498,7 @@
       <c r="A94" t="inlineStr"/>
       <c r="B94" t="inlineStr">
         <is>
-          <t>KAZR</t>
+          <t>MTLS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr"/>
@@ -1520,7 +1508,7 @@
       <c r="A95" t="inlineStr"/>
       <c r="B95" t="inlineStr">
         <is>
-          <t>KE</t>
+          <t>MYGN</t>
         </is>
       </c>
       <c r="C95" t="inlineStr"/>
@@ -1530,7 +1518,7 @@
       <c r="A96" t="inlineStr"/>
       <c r="B96" t="inlineStr">
         <is>
-          <t>KRT</t>
+          <t>NBIS</t>
         </is>
       </c>
       <c r="C96" t="inlineStr"/>
@@ -1540,7 +1528,7 @@
       <c r="A97" t="inlineStr"/>
       <c r="B97" t="inlineStr">
         <is>
-          <t>LGND</t>
+          <t>NNBR</t>
         </is>
       </c>
       <c r="C97" t="inlineStr"/>
@@ -1550,7 +1538,7 @@
       <c r="A98" t="inlineStr"/>
       <c r="B98" t="inlineStr">
         <is>
-          <t>LTRX</t>
+          <t>NTAP</t>
         </is>
       </c>
       <c r="C98" t="inlineStr"/>
@@ -1560,7 +1548,7 @@
       <c r="A99" t="inlineStr"/>
       <c r="B99" t="inlineStr">
         <is>
-          <t>MAR</t>
+          <t>NTNX</t>
         </is>
       </c>
       <c r="C99" t="inlineStr"/>
@@ -1570,7 +1558,7 @@
       <c r="A100" t="inlineStr"/>
       <c r="B100" t="inlineStr">
         <is>
-          <t>MBINM</t>
+          <t>NTRBW</t>
         </is>
       </c>
       <c r="C100" t="inlineStr"/>
@@ -1580,7 +1568,7 @@
       <c r="A101" t="inlineStr"/>
       <c r="B101" t="inlineStr">
         <is>
-          <t>MDWD</t>
+          <t>NVDA</t>
         </is>
       </c>
       <c r="C101" t="inlineStr"/>
@@ -1590,7 +1578,7 @@
       <c r="A102" t="inlineStr"/>
       <c r="B102" t="inlineStr">
         <is>
-          <t>MIRA</t>
+          <t>NVEC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr"/>
@@ -1600,7 +1588,7 @@
       <c r="A103" t="inlineStr"/>
       <c r="B103" t="inlineStr">
         <is>
-          <t>MKTW</t>
+          <t>NWGL</t>
         </is>
       </c>
       <c r="C103" t="inlineStr"/>
@@ -1610,7 +1598,7 @@
       <c r="A104" t="inlineStr"/>
       <c r="B104" t="inlineStr">
         <is>
-          <t>MLCI</t>
+          <t>NXXT</t>
         </is>
       </c>
       <c r="C104" t="inlineStr"/>
@@ -1620,7 +1608,7 @@
       <c r="A105" t="inlineStr"/>
       <c r="B105" t="inlineStr">
         <is>
-          <t>MYGN</t>
+          <t>OLLI</t>
         </is>
       </c>
       <c r="C105" t="inlineStr"/>
@@ -1630,7 +1618,7 @@
       <c r="A106" t="inlineStr"/>
       <c r="B106" t="inlineStr">
         <is>
-          <t>NDSN</t>
+          <t>OPRX</t>
         </is>
       </c>
       <c r="C106" t="inlineStr"/>
@@ -1640,7 +1628,7 @@
       <c r="A107" t="inlineStr"/>
       <c r="B107" t="inlineStr">
         <is>
-          <t>NSTS</t>
+          <t>ORBS</t>
         </is>
       </c>
       <c r="C107" t="inlineStr"/>
@@ -1650,7 +1638,7 @@
       <c r="A108" t="inlineStr"/>
       <c r="B108" t="inlineStr">
         <is>
-          <t>NTAP</t>
+          <t>OXBR</t>
         </is>
       </c>
       <c r="C108" t="inlineStr"/>
@@ -1660,7 +1648,7 @@
       <c r="A109" t="inlineStr"/>
       <c r="B109" t="inlineStr">
         <is>
-          <t>NTNX</t>
+          <t>OXLCZ</t>
         </is>
       </c>
       <c r="C109" t="inlineStr"/>
@@ -1670,7 +1658,7 @@
       <c r="A110" t="inlineStr"/>
       <c r="B110" t="inlineStr">
         <is>
-          <t>NVDA</t>
+          <t>PAAI</t>
         </is>
       </c>
       <c r="C110" t="inlineStr"/>
@@ -1680,7 +1668,7 @@
       <c r="A111" t="inlineStr"/>
       <c r="B111" t="inlineStr">
         <is>
-          <t>NVEC</t>
+          <t>PCAP</t>
         </is>
       </c>
       <c r="C111" t="inlineStr"/>
@@ -1690,7 +1678,7 @@
       <c r="A112" t="inlineStr"/>
       <c r="B112" t="inlineStr">
         <is>
-          <t>NXXT</t>
+          <t>PGEN</t>
         </is>
       </c>
       <c r="C112" t="inlineStr"/>
@@ -1700,7 +1688,7 @@
       <c r="A113" t="inlineStr"/>
       <c r="B113" t="inlineStr">
         <is>
-          <t>OCCIN</t>
+          <t>PLTR</t>
         </is>
       </c>
       <c r="C113" t="inlineStr"/>
@@ -1710,7 +1698,7 @@
       <c r="A114" t="inlineStr"/>
       <c r="B114" t="inlineStr">
         <is>
-          <t>OLLI</t>
+          <t>PLXS</t>
         </is>
       </c>
       <c r="C114" t="inlineStr"/>
@@ -1720,7 +1708,7 @@
       <c r="A115" t="inlineStr"/>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ONC</t>
+          <t>POWW</t>
         </is>
       </c>
       <c r="C115" t="inlineStr"/>
@@ -1730,7 +1718,7 @@
       <c r="A116" t="inlineStr"/>
       <c r="B116" t="inlineStr">
         <is>
-          <t>ORIC</t>
+          <t>PSHG</t>
         </is>
       </c>
       <c r="C116" t="inlineStr"/>
@@ -1740,7 +1728,7 @@
       <c r="A117" t="inlineStr"/>
       <c r="B117" t="inlineStr">
         <is>
-          <t>OXLCI</t>
+          <t>PSIG</t>
         </is>
       </c>
       <c r="C117" t="inlineStr"/>
@@ -1750,7 +1738,7 @@
       <c r="A118" t="inlineStr"/>
       <c r="B118" t="inlineStr">
         <is>
-          <t>OXLCM</t>
+          <t>PXLW</t>
         </is>
       </c>
       <c r="C118" t="inlineStr"/>
@@ -1760,7 +1748,7 @@
       <c r="A119" t="inlineStr"/>
       <c r="B119" t="inlineStr">
         <is>
-          <t>P</t>
+          <t>QMCO</t>
         </is>
       </c>
       <c r="C119" t="inlineStr"/>
@@ -1770,7 +1758,7 @@
       <c r="A120" t="inlineStr"/>
       <c r="B120" t="inlineStr">
         <is>
-          <t>PAAI</t>
+          <t>QNBC</t>
         </is>
       </c>
       <c r="C120" t="inlineStr"/>
@@ -1780,7 +1768,7 @@
       <c r="A121" t="inlineStr"/>
       <c r="B121" t="inlineStr">
         <is>
-          <t>PACH</t>
+          <t>QRVO</t>
         </is>
       </c>
       <c r="C121" t="inlineStr"/>
@@ -1790,7 +1778,7 @@
       <c r="A122" t="inlineStr"/>
       <c r="B122" t="inlineStr">
         <is>
-          <t>PANW</t>
+          <t>QTRX</t>
         </is>
       </c>
       <c r="C122" t="inlineStr"/>
@@ -1800,7 +1788,7 @@
       <c r="A123" t="inlineStr"/>
       <c r="B123" t="inlineStr">
         <is>
-          <t>PDFS</t>
+          <t>RCMT</t>
         </is>
       </c>
       <c r="C123" t="inlineStr"/>
@@ -1810,7 +1798,7 @@
       <c r="A124" t="inlineStr"/>
       <c r="B124" t="inlineStr">
         <is>
-          <t>PFLA</t>
+          <t>RGS</t>
         </is>
       </c>
       <c r="C124" t="inlineStr"/>
@@ -1820,7 +1808,7 @@
       <c r="A125" t="inlineStr"/>
       <c r="B125" t="inlineStr">
         <is>
-          <t>PGEN</t>
+          <t>RMTI</t>
         </is>
       </c>
       <c r="C125" t="inlineStr"/>
@@ -1830,7 +1818,7 @@
       <c r="A126" t="inlineStr"/>
       <c r="B126" t="inlineStr">
         <is>
-          <t>PHOS</t>
+          <t>RUSHB</t>
         </is>
       </c>
       <c r="C126" t="inlineStr"/>
@@ -1840,7 +1828,7 @@
       <c r="A127" t="inlineStr"/>
       <c r="B127" t="inlineStr">
         <is>
-          <t>PI</t>
+          <t>RVSB</t>
         </is>
       </c>
       <c r="C127" t="inlineStr"/>
@@ -1850,7 +1838,7 @@
       <c r="A128" t="inlineStr"/>
       <c r="B128" t="inlineStr">
         <is>
-          <t>PLPC</t>
+          <t>RWAYL</t>
         </is>
       </c>
       <c r="C128" t="inlineStr"/>
@@ -1860,7 +1848,7 @@
       <c r="A129" t="inlineStr"/>
       <c r="B129" t="inlineStr">
         <is>
-          <t>PLTR</t>
+          <t>RXRX</t>
         </is>
       </c>
       <c r="C129" t="inlineStr"/>
@@ -1870,7 +1858,7 @@
       <c r="A130" t="inlineStr"/>
       <c r="B130" t="inlineStr">
         <is>
-          <t>PNTG</t>
+          <t>SAFT</t>
         </is>
       </c>
       <c r="C130" t="inlineStr"/>
@@ -1880,7 +1868,7 @@
       <c r="A131" t="inlineStr"/>
       <c r="B131" t="inlineStr">
         <is>
-          <t>PPIH</t>
+          <t>SAIL</t>
         </is>
       </c>
       <c r="C131" t="inlineStr"/>
@@ -1890,7 +1878,7 @@
       <c r="A132" t="inlineStr"/>
       <c r="B132" t="inlineStr">
         <is>
-          <t>PPSI</t>
+          <t>SBMT</t>
         </is>
       </c>
       <c r="C132" t="inlineStr"/>
@@ -1900,7 +1888,7 @@
       <c r="A133" t="inlineStr"/>
       <c r="B133" t="inlineStr">
         <is>
-          <t>PS</t>
+          <t>SGHT</t>
         </is>
       </c>
       <c r="C133" t="inlineStr"/>
@@ -1910,7 +1898,7 @@
       <c r="A134" t="inlineStr"/>
       <c r="B134" t="inlineStr">
         <is>
-          <t>PSIG</t>
+          <t>SHMD</t>
         </is>
       </c>
       <c r="C134" t="inlineStr"/>
@@ -1920,7 +1908,7 @@
       <c r="A135" t="inlineStr"/>
       <c r="B135" t="inlineStr">
         <is>
-          <t>QNTM</t>
+          <t>SHOP</t>
         </is>
       </c>
       <c r="C135" t="inlineStr"/>
@@ -1930,7 +1918,7 @@
       <c r="A136" t="inlineStr"/>
       <c r="B136" t="inlineStr">
         <is>
-          <t>QTRX</t>
+          <t>SIMO</t>
         </is>
       </c>
       <c r="C136" t="inlineStr"/>
@@ -1940,7 +1928,7 @@
       <c r="A137" t="inlineStr"/>
       <c r="B137" t="inlineStr">
         <is>
-          <t>QUBT</t>
+          <t>SKYA</t>
         </is>
       </c>
       <c r="C137" t="inlineStr"/>
@@ -1950,7 +1938,7 @@
       <c r="A138" t="inlineStr"/>
       <c r="B138" t="inlineStr">
         <is>
-          <t>RCMT</t>
+          <t>SLAB</t>
         </is>
       </c>
       <c r="C138" t="inlineStr"/>
@@ -1960,7 +1948,7 @@
       <c r="A139" t="inlineStr"/>
       <c r="B139" t="inlineStr">
         <is>
-          <t>RDIB</t>
+          <t>SLMT</t>
         </is>
       </c>
       <c r="C139" t="inlineStr"/>
@@ -1970,7 +1958,7 @@
       <c r="A140" t="inlineStr"/>
       <c r="B140" t="inlineStr">
         <is>
-          <t>RDWR</t>
+          <t>SNPS</t>
         </is>
       </c>
       <c r="C140" t="inlineStr"/>
@@ -1980,7 +1968,7 @@
       <c r="A141" t="inlineStr"/>
       <c r="B141" t="inlineStr">
         <is>
-          <t>RGEN</t>
+          <t>SONO</t>
         </is>
       </c>
       <c r="C141" t="inlineStr"/>
@@ -1990,7 +1978,7 @@
       <c r="A142" t="inlineStr"/>
       <c r="B142" t="inlineStr">
         <is>
-          <t>RGS</t>
+          <t>SRZN</t>
         </is>
       </c>
       <c r="C142" t="inlineStr"/>
@@ -2000,7 +1988,7 @@
       <c r="A143" t="inlineStr"/>
       <c r="B143" t="inlineStr">
         <is>
-          <t>RIGL</t>
+          <t>SSYS</t>
         </is>
       </c>
       <c r="C143" t="inlineStr"/>
@@ -2010,7 +1998,7 @@
       <c r="A144" t="inlineStr"/>
       <c r="B144" t="inlineStr">
         <is>
-          <t>RILYN</t>
+          <t>STRC</t>
         </is>
       </c>
       <c r="C144" t="inlineStr"/>
@@ -2020,7 +2008,7 @@
       <c r="A145" t="inlineStr"/>
       <c r="B145" t="inlineStr">
         <is>
-          <t>RNW</t>
+          <t>STRF</t>
         </is>
       </c>
       <c r="C145" t="inlineStr"/>
@@ -2030,7 +2018,7 @@
       <c r="A146" t="inlineStr"/>
       <c r="B146" t="inlineStr">
         <is>
-          <t>SAIH</t>
+          <t>STRK</t>
         </is>
       </c>
       <c r="C146" t="inlineStr"/>
@@ -2040,7 +2028,7 @@
       <c r="A147" t="inlineStr"/>
       <c r="B147" t="inlineStr">
         <is>
-          <t>SBC</t>
+          <t>SUIG</t>
         </is>
       </c>
       <c r="C147" t="inlineStr"/>
@@ -2050,7 +2038,7 @@
       <c r="A148" t="inlineStr"/>
       <c r="B148" t="inlineStr">
         <is>
-          <t>SDGR</t>
+          <t>SVCO</t>
         </is>
       </c>
       <c r="C148" t="inlineStr"/>
@@ -2060,7 +2048,7 @@
       <c r="A149" t="inlineStr"/>
       <c r="B149" t="inlineStr">
         <is>
-          <t>SGHT</t>
+          <t>SVIA</t>
         </is>
       </c>
       <c r="C149" t="inlineStr"/>
@@ -2070,7 +2058,7 @@
       <c r="A150" t="inlineStr"/>
       <c r="B150" t="inlineStr">
         <is>
-          <t>SIMO</t>
+          <t>SVIAW</t>
         </is>
       </c>
       <c r="C150" t="inlineStr"/>
@@ -2080,7 +2068,7 @@
       <c r="A151" t="inlineStr"/>
       <c r="B151" t="inlineStr">
         <is>
-          <t>SLAB</t>
+          <t>SVRN</t>
         </is>
       </c>
       <c r="C151" t="inlineStr"/>
@@ -2090,7 +2078,7 @@
       <c r="A152" t="inlineStr"/>
       <c r="B152" t="inlineStr">
         <is>
-          <t>SMTI</t>
+          <t>SWRD</t>
         </is>
       </c>
       <c r="C152" t="inlineStr"/>
@@ -2100,7 +2088,7 @@
       <c r="A153" t="inlineStr"/>
       <c r="B153" t="inlineStr">
         <is>
-          <t>SOPH</t>
+          <t>TAOX</t>
         </is>
       </c>
       <c r="C153" t="inlineStr"/>
@@ -2110,7 +2098,7 @@
       <c r="A154" t="inlineStr"/>
       <c r="B154" t="inlineStr">
         <is>
-          <t>SQFTP</t>
+          <t>TCPC</t>
         </is>
       </c>
       <c r="C154" t="inlineStr"/>
@@ -2120,7 +2108,7 @@
       <c r="A155" t="inlineStr"/>
       <c r="B155" t="inlineStr">
         <is>
-          <t>STLN</t>
+          <t>TER</t>
         </is>
       </c>
       <c r="C155" t="inlineStr"/>
@@ -2130,7 +2118,7 @@
       <c r="A156" t="inlineStr"/>
       <c r="B156" t="inlineStr">
         <is>
-          <t>STRC</t>
+          <t>TITN</t>
         </is>
       </c>
       <c r="C156" t="inlineStr"/>
@@ -2140,7 +2128,7 @@
       <c r="A157" t="inlineStr"/>
       <c r="B157" t="inlineStr">
         <is>
-          <t>STRF</t>
+          <t>TKNO</t>
         </is>
       </c>
       <c r="C157" t="inlineStr"/>
@@ -2150,7 +2138,7 @@
       <c r="A158" t="inlineStr"/>
       <c r="B158" t="inlineStr">
         <is>
-          <t>STRK</t>
+          <t>TONX</t>
         </is>
       </c>
       <c r="C158" t="inlineStr"/>
@@ -2160,7 +2148,7 @@
       <c r="A159" t="inlineStr"/>
       <c r="B159" t="inlineStr">
         <is>
-          <t>SVRN</t>
+          <t>TWAV</t>
         </is>
       </c>
       <c r="C159" t="inlineStr"/>
@@ -2170,7 +2158,7 @@
       <c r="A160" t="inlineStr"/>
       <c r="B160" t="inlineStr">
         <is>
-          <t>SWKHL</t>
+          <t>VICR</t>
         </is>
       </c>
       <c r="C160" t="inlineStr"/>
@@ -2180,7 +2168,7 @@
       <c r="A161" t="inlineStr"/>
       <c r="B161" t="inlineStr">
         <is>
-          <t>TAYD</t>
+          <t>WLTH</t>
         </is>
       </c>
       <c r="C161" t="inlineStr"/>
@@ -2190,91 +2178,11 @@
       <c r="A162" t="inlineStr"/>
       <c r="B162" t="inlineStr">
         <is>
-          <t>TELO</t>
+          <t>XCBE</t>
         </is>
       </c>
       <c r="C162" t="inlineStr"/>
       <c r="D162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr"/>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>TEM</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr"/>
-      <c r="D163" t="inlineStr"/>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr"/>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>TLACU</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr"/>
-      <c r="D164" t="inlineStr"/>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr"/>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>TMS</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr"/>
-      <c r="D165" t="inlineStr"/>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr"/>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>TONT</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr"/>
-      <c r="D166" t="inlineStr"/>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr"/>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>TONX</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr"/>
-      <c r="D167" t="inlineStr"/>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr"/>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>TRLV</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr"/>
-      <c r="D168" t="inlineStr"/>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr"/>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>VAI</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr"/>
-      <c r="D169" t="inlineStr"/>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr"/>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>XXI</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr"/>
-      <c r="D170" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
